--- a/dados/candidatos.xlsx
+++ b/dados/candidatos.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -1658,6 +1658,39 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://alinsperedu-my.sharepoint.com/personal/alcidysapb_al_insper_edu_br/Documents/Apps/Microsoft%20Forms/Buddy%20Program%2020262%C2%A0-%20Processo%20seletivo/Compartilhe%20uma%20foto%20em%20algum%20momento%20Internaciona/dfe5c670-1ebb-46ad-b10a-53b2f4c891f0_Vince%20de%20Luca%20Liu.jpeg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rafaelama3@al.insper.edu.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rafaela de Moura Assis</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">266201443</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A minha maior motivação para participar do programa é a oportunidade de comunicação em outros idiomas e fazer laços baseado em empatia e acolhimento. O programa abrange um dos meus maiores interesses que, desde mais jovem, sempre foi baseado em conhecer pessoas do mundo inteiro. Aliado ao insper, acredito que o programa, fomente essa dinâmica entre pessoas diversas, e pode ser visto como um pilar para conhecer novas culturas e também compartilhar a nossa cultura brasileira e vivências da faculdade. Acredito no meu potencial, já que um dos meus maiores hobbies, além de estudar inglês, espanhol, italiano, japonês, inclui também conversar sobre vivência, rotina, adaptação e cultura no geral. Também acredito que, de minha parte, pode se esperar grande engajamento, participação e compromisso tanto pelas motivações baseadas em gostos, como também pelo interesse em proporcionar uma boa experiência no insper aos novos alunos estrangeiros.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://alinsperedu-my.sharepoint.com/personal/alcidysapb_al_insper_edu_br/Documents/Apps/Microsoft%20Forms/Buddy%20Program%2020262%C2%A0-%20Processo%20seletivo/Compartilhe%20uma%20foto%20em%20algum%20momento%20Internaciona/image_Rafaela%20de%20Moura%20Ass.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">luisafov@al.insper.edu.br</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Luisa Farias de Oliveira Valente</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Luísa Farias de Oliveira Valente</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26610549</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">O Buddy Program foi algo que sempre me interessou. Desde antes de ingressar na faculdade, a ideia de conhecer pessoas de outros países e ajudá-las a se ambientar na faculdade e no país me parecia muito legal. Assim que entrei na faculdade, procurei saber sobre o programa, porém resolvi esperar para me acostumar e me ambientar na cidade e na faculdade antes de procurar prestar apoio a outras pessoas nesses quesitos. Espero conseguir conhecer e ter contato com diversas culturas através dos intercambistas, fazer novas amizades e ter a oportunidade de ajudar outras pessoas a conhecerem e se acostumarem com o Brasil e, principalmente, com o Insper, que eu amo, mas entendo e lembro como é assustador no início. Para agregar ao programa da melhor forma possível, me colocarei à disposição o semestre inteiro para os estrangeiros, para prestar apoio como puder. Tentarei convidá-los para sairmos tanto pela cidade, fora do horário de aula, como no dia a dia, almoçando juntos, estudando juntos etc., se eles quiserem. Irei, principalmente, me esforçar ao máximo para fazê-los se sentirem confortáveis o bastante para aproveitarem ao máximo o seu intercâmbio.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://alinsperedu-my.sharepoint.com/personal/alcidysapb_al_insper_edu_br/Documents/Apps/Microsoft%20Forms/Buddy%20Program%2020262%C2%A0-%20Processo%20seletivo/Compartilhe%20uma%20foto%20em%20algum%20momento%20Internaciona/WhatsApp%20Image%202026-10-06%20at%2021.07.21_Luisa%20Farias%20de%20Oliv.jpeg</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1754,8 +1787,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:P85" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:P85"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:P87" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:P87"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Hora de início" dataDxfId="3"/>
@@ -6178,11 +6211,107 @@
         <x:v>499</x:v>
       </x:c>
     </x:row>
+    <x:row r="86" hidden="0">
+      <x:c r="A86">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B86" s="2">
+        <x:v>46301.75491898148</x:v>
+      </x:c>
+      <x:c r="C86" s="2">
+        <x:v>46301.76021990741</x:v>
+      </x:c>
+      <x:c r="D86" s="10" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E86" s="10" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="F86" s="2"/>
+      <x:c r="G86" s="10" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="H86" s="10" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="I86" s="7" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="J86" s="10" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="K86" s="10" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L86" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="M86" s="10" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="N86" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="O86" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P86" s="10" t="s">
+        <x:v>504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" hidden="0">
+      <x:c r="A87">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B87" s="2">
+        <x:v>46301.77173611111</x:v>
+      </x:c>
+      <x:c r="C87" s="2">
+        <x:v>46301.88125</x:v>
+      </x:c>
+      <x:c r="D87" s="10" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="E87" s="10" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="F87" s="2"/>
+      <x:c r="G87" s="10" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="H87" s="10" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="I87" s="7" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="J87" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K87" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L87" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="M87" s="10" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="N87" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="O87" s="10" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="P87" s="10" t="s">
+        <x:v>510</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R0698561a4b974355"/>
+    <x:tablePart r:id="R713d47765fc34f63"/>
   </x:tableParts>
 </x:worksheet>
 </file>